--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -1,48 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\do_not_use_modules_report\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA0D092-5E97-44DB-B39C-5D9742B0FF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DisabledModules" sheetId="1" r:id="rId1"/>
+    <sheet name="DisabledModules" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DisabledModules!$A$8:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DisabledModules!$A$8:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>Disabled Modules</t>
-  </si>
-  <si>
-    <t>Date Range:  &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>&lt;StatesLabel&gt;:  &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t xml:space="preserve">Disabled Modules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;StatesLabel&gt;:  &lt;States&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of Distinct Disabled Modules:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -51,19 +43,22 @@
     <t>#</t>
   </si>
   <si>
-    <t>Device Name</t>
-  </si>
-  <si>
-    <t>Module Name</t>
-  </si>
-  <si>
-    <t>Module Serial</t>
+    <t xml:space="preserve">Device Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module Serial</t>
   </si>
   <si>
     <t xml:space="preserve">Date Marked as 'Do Not Use' </t>
   </si>
   <si>
-    <t>Total Tests Run</t>
+    <t xml:space="preserve">Total Tests Run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Test Uploaded Date</t>
   </si>
   <si>
     <t>&lt;#&gt;</t>
@@ -82,44 +77,37 @@
   </si>
   <si>
     <t>&lt;totalTestsRun&gt;</t>
+  </si>
+  <si>
+    <t>&lt;lastTestUploadedDate&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
+      <sz val="16.000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="12.000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -132,17 +120,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF3CC0DD"/>
-        <bgColor rgb="FF00CCFF"/>
+        <bgColor indexed="40"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -157,7 +145,20 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
@@ -172,102 +173,37 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="3" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="2" fillId="0" borderId="3" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -279,8 +215,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -322,108 +541,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -431,7 +556,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -457,7 +582,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -509,16 +634,28 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -534,7 +671,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -565,65 +702,63 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" customWidth="1"/>
-    <col min="16384" max="16384" width="10.109375" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="6.5546875"/>
+    <col customWidth="1" min="2" max="2" width="28.6640625"/>
+    <col customWidth="1" min="3" max="3" width="18.77734375"/>
+    <col customWidth="1" min="4" max="4" width="20.33203125"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="33"/>
+    <col customWidth="1" min="6" max="6" width="20.77734375"/>
+    <col customWidth="1" min="7" max="7" width="28.00390625"/>
+    <col customWidth="1" min="8" max="16384" width="10.109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" ht="16.5">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" ht="16.5">
       <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="F3">
+        <f>IF(COUNTA(D9:D100000)=0,0,SUM(1/COUNTIF(D9:D100000,D9:D100000)))</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" ht="16.5">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" ht="16.5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" ht="16.5">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -642,30 +777,38 @@
       <c r="F8" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="G8" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="s">
+    <row r="9" ht="16.5">
+      <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>17</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:F9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <autoFilter ref="A8:G8"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -9,7 +9,7 @@
     <sheet name="DisabledModules" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DisabledModules!$A$8:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DisabledModules!$A$8:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DisabledModules!$A$8:$G$8</definedName>
   </definedNames>
   <calcPr/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">Disabled Modules</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t xml:space="preserve">Count of Distinct Disabled Modules:</t>
+  </si>
+  <si>
+    <t>&lt;countOfDistinctDisabledModules&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
@@ -736,72 +739,71 @@
       <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="F3">
-        <f>IF(COUNTA(D9:D100000)=0,0,SUM(1/COUNTIF(D9:D100000,D9:D100000)))</f>
-        <v>1</v>
+      <c r="F3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="16.5">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" ht="16.5">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="16.5">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="16.5">
       <c r="A9" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -1,43 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/do_not_use_modules_report/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D8C70D-3BAB-B74A-83A2-64A6FD3B4EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DisabledModules" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Disabled Modules" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DisabledModules!$A$8:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DisabledModules!$A$8:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disabled Modules'!$A$8:$G$8</definedName>
   </definedNames>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
-    <t xml:space="preserve">Disabled Modules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;StatesLabel&gt;:  &lt;States&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count of Distinct Disabled Modules:</t>
+    <t>Disabled Modules</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;:  &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Count of Distinct Disabled Modules:</t>
   </si>
   <si>
     <t>&lt;countOfDistinctDisabledModules&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -46,22 +49,22 @@
     <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">Device Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Module Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Module Serial</t>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Module Serial</t>
   </si>
   <si>
     <t xml:space="preserve">Date Marked as 'Do Not Use' </t>
   </si>
   <si>
-    <t xml:space="preserve">Total Tests Run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Test Uploaded Date</t>
+    <t>Total Tests Run</t>
+  </si>
+  <si>
+    <t>Last Test Uploaded Date</t>
   </si>
   <si>
     <t>&lt;#&gt;</t>
@@ -88,29 +91,29 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.000000"/>
+      <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -129,11 +132,11 @@
   </fills>
   <borders count="4">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -148,7 +151,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -160,8 +163,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -176,31 +179,30 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="3" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -218,291 +220,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -705,33 +424,35 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="6.5546875"/>
-    <col customWidth="1" min="2" max="2" width="28.6640625"/>
-    <col customWidth="1" min="3" max="3" width="18.77734375"/>
-    <col customWidth="1" min="4" max="4" width="20.33203125"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="33"/>
-    <col customWidth="1" min="6" max="6" width="20.77734375"/>
-    <col customWidth="1" min="7" max="7" width="28.00390625"/>
-    <col customWidth="1" min="8" max="16384" width="10.109375"/>
+    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" ht="16.5">
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" ht="16.5">
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -743,24 +464,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="16.5">
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" ht="16.5">
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="16.5">
+    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -783,23 +504,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" ht="16.5">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -807,10 +528,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:G8"/>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <autoFilter ref="A8:G8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/do_not_use_modules_report/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D8C70D-3BAB-B74A-83A2-64A6FD3B4EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580"/>
   </bookViews>
   <sheets>
-    <sheet name="Disabled Modules" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Disabled Modules" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Disabled Modules'!$A$8:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase">'Disabled Modules'!$A$8:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Disabled Modules</t>
   </si>
@@ -52,6 +46,9 @@
     <t>Device Name</t>
   </si>
   <si>
+    <t>Site</t>
+  </si>
+  <si>
     <t>Module Name</t>
   </si>
   <si>
@@ -71,6 +68,9 @@
   </si>
   <si>
     <t>&lt;deviceName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;moduleName&gt;</t>
@@ -91,29 +91,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="16"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -139,46 +141,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -429,30 +409,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="10.1640625"/>
   <cols>
-    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="33" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -464,24 +444,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -494,42 +474,50 @@
       <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
+      <c r="G9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A8:G8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <autoFilter ref="A8:G8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0463594-971F-1D4D-8076-D013FA46C76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Disabled Modules" state="visible" r:id="rId4"/>
+    <sheet name="Disabled Modules" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Disabled Modules'!$A$8:$G$8</definedName>
@@ -91,31 +92,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="16"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -141,24 +142,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -409,13 +432,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="10.1640625"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="36.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" customWidth="1"/>
     <col min="6" max="6" width="33" customWidth="1"/>
@@ -423,16 +446,16 @@
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -444,24 +467,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -487,7 +510,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
@@ -513,11 +536,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A8:G8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <autoFilter ref="A8:G8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0463594-971F-1D4D-8076-D013FA46C76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="21580"/>
   </bookViews>
   <sheets>
-    <sheet name="Disabled Modules" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Disabled Modules" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'Disabled Modules'!$A$8:$G$8</definedName>
@@ -18,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Disabled Modules</t>
   </si>
@@ -36,6 +35,9 @@
   </si>
   <si>
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -92,31 +94,31 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="16"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -142,46 +144,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -432,9 +412,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="10.1640625"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -446,16 +426,16 @@
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -467,78 +447,83 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:G8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <autoFilter ref="A8:G8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.5118110236220469" footer="0.5118110236220469"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -168,10 +168,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -460,7 +461,7 @@
       <c r="B5" s="2"/>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -470,54 +471,54 @@
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
     </row>

--- a/api/templates/do_not_use_modules_report/en.xlsx
+++ b/api/templates/do_not_use_modules_report/en.xlsx
@@ -37,7 +37,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -168,11 +168,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -461,7 +460,7 @@
       <c r="B5" s="2"/>
     </row>
     <row r="6" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -471,54 +470,54 @@
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>23</v>
       </c>
     </row>
